--- a/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,11</t>
+          <t>0,0; 40,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 45,46</t>
+          <t>5,48; 47,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,41</t>
+          <t>0,0; 55,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,58</t>
+          <t>0,0; 20,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,59</t>
+          <t>0,0; 36,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 24,38</t>
+          <t>2,65; 22,39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,79; 43,54</t>
+          <t>5,74; 43,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,37; 48,26</t>
+          <t>5,43; 48,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,72</t>
+          <t>0,0; 45,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,87</t>
+          <t>0,0; 25,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 32,16</t>
+          <t>3,91; 34,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 24,62</t>
+          <t>4,72; 25,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,15</t>
+          <t>0,0; 41,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,57</t>
+          <t>0,0; 28,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,43</t>
+          <t>0,0; 47,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,13</t>
+          <t>0,0; 38,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,32</t>
+          <t>0,0; 34,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 50,87</t>
+          <t>6,39; 50,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 34,24</t>
+          <t>3,37; 31,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,04</t>
+          <t>0,0; 27,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 25,88</t>
+          <t>3,19; 26,92</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,55</t>
+          <t>0,0; 43,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,21</t>
+          <t>0,0; 61,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,52</t>
+          <t>0,0; 32,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,52</t>
+          <t>0,0; 43,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,42 +1228,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,38</t>
+          <t>0,0; 42,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,28</t>
+          <t>0,0; 27,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1274,7 +1275,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,6</t>
+          <t>0,0; 44,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,1</t>
+          <t>0,0; 82,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,77</t>
+          <t>0,0; 55,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,63</t>
+          <t>0,0; 61,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,15</t>
+          <t>0,0; 35,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,52</t>
+          <t>0,0; 21,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,11</t>
+          <t>0,0; 37,8</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,23</t>
+          <t>0,0; 27,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,27</t>
+          <t>0,0; 45,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,65</t>
+          <t>0,0; 17,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,7</t>
+          <t>0,0; 28,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 16,44</t>
+          <t>3,53; 15,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,81</t>
+          <t>3,11; 14,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 13,5</t>
+          <t>2,23; 13,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,5</t>
+          <t>2,82; 15,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 18,66</t>
+          <t>5,23; 18,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 13,32</t>
+          <t>1,56; 14,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,09; 12,7</t>
+          <t>3,87; 12,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,81</t>
+          <t>5,16; 13,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 11,29</t>
+          <t>3,25; 11,17</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1740</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2319</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>502; 4378</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4590</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2754</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4781</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>511; 4321</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2584</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>592; 4482</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>660; 5880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>631; 5493</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1230; 6729</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3047</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4370</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3073</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2813</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>619; 4907</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>493; 4659</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4031</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>623; 5255</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1520</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 1952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3885</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4784</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2737</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2227</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2865</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2495</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2623</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3333</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3361</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2974</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4158</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2841</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4081</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1639</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3800</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4668</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3396</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4955</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>10792</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>6486</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1551; 6800</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>1903; 8644</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>1229; 7367</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>1315; 7394</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3324; 11862</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>748; 6722</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3509; 11239</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>6442; 17051</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3348; 11500</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,49</t>
+          <t>0,0; 45,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 47,76</t>
+          <t>5,26; 46,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,79</t>
+          <t>0,0; 55,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,22</t>
+          <t>0,0; 19,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,3</t>
+          <t>0,0; 36,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 22,39</t>
+          <t>2,66; 24,74</t>
         </is>
       </c>
     </row>
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 43,48</t>
+          <t>5,68; 42,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 48,44</t>
+          <t>5,28; 42,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,46</t>
+          <t>0,0; 55,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,28</t>
+          <t>0,0; 18,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 34,06</t>
+          <t>3,88; 34,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 25,84</t>
+          <t>4,73; 24,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,85</t>
+          <t>0,0; 51,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,56</t>
+          <t>0,0; 22,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,63</t>
+          <t>0,0; 49,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,38</t>
+          <t>0,0; 38,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,43</t>
+          <t>0,0; 33,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,39; 50,68</t>
+          <t>6,15; 46,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 31,86</t>
+          <t>3,4; 29,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,08</t>
+          <t>0,0; 28,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 26,92</t>
+          <t>3,2; 25,86</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,26</t>
+          <t>0,0; 56,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,01</t>
+          <t>0,0; 59,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,42</t>
+          <t>0,0; 30,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,48</t>
+          <t>0,0; 39,74</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,65</t>
+          <t>0,0; 56,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,93</t>
+          <t>0,0; 34,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,08</t>
+          <t>0,0; 50,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1358,27 +1358,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,65</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,36</t>
+          <t>0,0; 66,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,8</t>
+          <t>0,0; 33,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,53</t>
+          <t>0,0; 21,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,8</t>
+          <t>0,0; 39,03</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,35</t>
+          <t>0,0; 24,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,09</t>
+          <t>0,0; 42,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,24</t>
+          <t>0,0; 17,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,75</t>
+          <t>0,0; 28,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 15,5</t>
+          <t>2,65; 15,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,1</t>
+          <t>2,58; 13,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 13,36</t>
+          <t>3,05; 14,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,83</t>
+          <t>2,83; 14,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 18,66</t>
+          <t>4,84; 17,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,05</t>
+          <t>1,58; 13,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,87; 12,41</t>
+          <t>4,04; 12,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,66</t>
+          <t>5,23; 13,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,17</t>
+          <t>3,19; 10,73</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por diarrea o problemas intestinales (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2319</t>
+          <t>0; 2629</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502; 4378</t>
+          <t>483; 4269</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4590</t>
+          <t>0; 4573</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2754</t>
+          <t>0; 2718</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4781</t>
+          <t>0; 4777</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>511; 4321</t>
+          <t>513; 4776</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>592; 4482</t>
+          <t>586; 4349</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>660; 5880</t>
+          <t>641; 5199</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 3252</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 2575</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>631; 5493</t>
+          <t>627; 5577</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1230; 6729</t>
+          <t>1233; 6278</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3047</t>
+          <t>0; 3755</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4370</t>
+          <t>0; 3469</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3073</t>
+          <t>0; 3220</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 3262</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2813</t>
+          <t>0; 2756</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,22 +2375,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>619; 4907</t>
+          <t>596; 4519</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>493; 4659</t>
+          <t>496; 4309</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 4181</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>623; 5255</t>
+          <t>625; 5049</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1952</t>
+          <t>0; 2571</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 3763</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4564</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2737</t>
+          <t>0; 2502</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2227</t>
+          <t>0; 2933</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2865</t>
+          <t>0; 3561</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2623</t>
+          <t>0; 3030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2859,27 +2859,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3361</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2974</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 4158</t>
+          <t>0; 3834</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2841</t>
+          <t>0; 2787</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4081</t>
+          <t>0; 4214</t>
         </is>
       </c>
     </row>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4668</t>
+          <t>0; 4407</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3396</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4955</t>
+          <t>0; 4840</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1551; 6800</t>
+          <t>1161; 6945</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1903; 8644</t>
+          <t>1579; 8390</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1229; 7367</t>
+          <t>1679; 7863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1315; 7394</t>
+          <t>1320; 6767</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3324; 11862</t>
+          <t>3074; 11413</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>748; 6722</t>
+          <t>755; 6453</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3509; 11239</t>
+          <t>3659; 11402</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6442; 17051</t>
+          <t>6535; 16554</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3348; 11500</t>
+          <t>3286; 11046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$diarrea-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,58%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>18,98%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 58,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 46,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,33; 45,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,96</t>
+          <t>0,0; 18,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,27</t>
+          <t>0,0; 34,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 24,74</t>
+          <t>2,69; 24,38</t>
         </is>
       </c>
     </row>
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>21,29%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,68; 42,19</t>
+          <t>0,0; 54,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 42,83</t>
+          <t>0,0; 22,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,87</t>
+          <t>5,79; 43,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,52</t>
+          <t>5,37; 48,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,88; 34,58</t>
+          <t>3,9; 32,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 24,11</t>
+          <t>4,85; 24,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -850,22 +850,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 52,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,67</t>
+          <t>0,0; 24,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>21,15%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9,62%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,91</t>
+          <t>0,0; 34,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,18; 50,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,72</t>
+          <t>0,0; 54,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 46,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 29,47</t>
+          <t>3,5; 34,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,08</t>
+          <t>0,0; 27,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 25,86</t>
+          <t>3,2; 25,88</t>
         </is>
       </c>
     </row>
@@ -1070,27 +1070,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,23%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,92</t>
+          <t>0,0; 32,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,74</t>
+          <t>0,0; 40,52</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1180,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>13,44%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,72</t>
+          <t>0,0; 30,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10,69%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10,3%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34,01%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 82,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 45,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,92</t>
+          <t>0,0; 60,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,52</t>
+          <t>0,0; 44,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,01</t>
+          <t>0,0; 36,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,12</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,03</t>
+          <t>0,0; 38,11</t>
         </is>
       </c>
     </row>
@@ -1395,27 +1395,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 44,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,31</t>
+          <t>0,0; 17,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,09</t>
+          <t>0,0; 29,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>10,52%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 15,83</t>
+          <t>2,8; 15,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 13,69</t>
+          <t>4,42; 18,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 14,26</t>
+          <t>1,61; 13,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 14,49</t>
+          <t>3,47; 16,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,96</t>
+          <t>2,43; 14,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,58; 13,48</t>
+          <t>2,55; 13,5</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 12,59</t>
+          <t>4,09; 12,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 13,26</t>
+          <t>5,33; 13,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 10,73</t>
+          <t>3,23; 11,29</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1740</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1529</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2629</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4805</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>483; 4269</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4573</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>488; 4167</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2718</t>
+          <t>0; 2531</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4777</t>
+          <t>0; 4556</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>513; 4776</t>
+          <t>520; 4706</t>
         </is>
       </c>
     </row>
@@ -1918,27 +1918,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1971,27 +1971,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1866</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2584</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>586; 4349</t>
+          <t>0; 3185</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>641; 5199</t>
+          <t>0; 3181</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3252</t>
+          <t>597; 4488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2575</t>
+          <t>652; 5858</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>627; 5577</t>
+          <t>629; 5187</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1233; 6278</t>
+          <t>1262; 6412</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3796</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3755</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3469</t>
+          <t>0; 3759</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2244,32 +2244,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2048</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1047</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>822</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 2805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3262</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>599; 4926</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2756</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>596; 4519</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>496; 4309</t>
+          <t>512; 5007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4181</t>
+          <t>0; 4026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>625; 5049</t>
+          <t>624; 5052</t>
         </is>
       </c>
     </row>
@@ -2412,27 +2412,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2465,27 +2465,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>597</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3771</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2571</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3763</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2551</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2548,12 +2548,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4564</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2502</t>
+          <t>0; 2551</t>
         </is>
       </c>
     </row>
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>702</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>729</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2933</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3561</t>
+          <t>0; 3106</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3320</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2765</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3030</t>
+          <t>0; 2939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3333</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3224</t>
+          <t>0; 2654</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3834</t>
+          <t>0; 4199</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2787</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4214</t>
+          <t>0; 4116</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2949,12 +2949,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>686</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4582</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 4407</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 3410</t>
+          <t>0; 3475</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4840</t>
+          <t>0; 5119</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>4108</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>3679</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>3370</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6684</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1161; 6945</t>
+          <t>1308; 7239</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1579; 8390</t>
+          <t>2807; 11859</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1679; 7863</t>
+          <t>772; 6375</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1320; 6767</t>
+          <t>1525; 7215</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3074; 11413</t>
+          <t>1487; 9075</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>755; 6453</t>
+          <t>1408; 7444</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3659; 11402</t>
+          <t>3704; 11500</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6535; 16554</t>
+          <t>6653; 17248</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3286; 11046</t>
+          <t>3330; 11631</t>
         </is>
       </c>
     </row>
